--- a/03_Outputs/Rio_Grande/05_Economia/economia.xlsx
+++ b/03_Outputs/Rio_Grande/05_Economia/economia.xlsx
@@ -7454,10 +7454,8 @@
       <c r="F3" s="118">
         <v>115.608571123879</v>
       </c>
-      <c r="G3" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G3" s="120">
+        <v>0.01014506316</v>
       </c>
       <c r="H3" s="122">
         <v>34.88956477311</v>
@@ -7574,10 +7572,8 @@
       <c r="F5" s="118">
         <v>102.805831415529</v>
       </c>
-      <c r="G5" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G5" s="120">
+        <v>0.00728054617000003</v>
       </c>
       <c r="H5" s="122">
         <v>294.49228659261</v>
@@ -7697,7 +7693,7 @@
         <v>454.678948165257</v>
       </c>
       <c r="G7" s="121">
-        <v>0.465297466210002</v>
+        <v>0.482723075540002</v>
       </c>
       <c r="H7" s="123">
         <v>558.860236803241</v>
@@ -7755,10 +7751,8 @@
       <c r="F8" s="118">
         <v>13.8560529607089</v>
       </c>
-      <c r="G8" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8" s="120">
+        <v>0.00114208958505699</v>
       </c>
       <c r="H8" s="122">
         <v>4.07693331951311</v>
@@ -7816,10 +7810,8 @@
       <c r="F9" s="118">
         <v>121.340088922525</v>
       </c>
-      <c r="G9" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G9" s="120">
+        <v>0.00174762481123468</v>
       </c>
       <c r="H9" s="122">
         <v>35.8420607967678</v>
@@ -7936,10 +7928,8 @@
       <c r="F11" s="118">
         <v>84.4338596706688</v>
       </c>
-      <c r="G11" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G11" s="120">
+        <v>0.00599807955792014</v>
       </c>
       <c r="H11" s="122">
         <v>375.605509001628</v>
@@ -8059,7 +8049,7 @@
         <v>490.206376098047</v>
       </c>
       <c r="G13" s="121">
-        <v>2.10634769425951</v>
+        <v>2.11523548821372</v>
       </c>
       <c r="H13" s="123">
         <v>653.020035551639</v>
@@ -8176,10 +8166,8 @@
       <c r="F15" s="118">
         <v>135.558003809801</v>
       </c>
-      <c r="G15" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G15" s="120">
+        <v>0.00282569366403166</v>
       </c>
       <c r="H15" s="122">
         <v>38.0377703889468</v>
@@ -8296,10 +8284,8 @@
       <c r="F17" s="118">
         <v>49.4103290270382</v>
       </c>
-      <c r="G17" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G17" s="120">
+        <v>0.00202112019860218</v>
       </c>
       <c r="H17" s="122">
         <v>378.531990802643</v>
@@ -8419,7 +8405,7 @@
         <v>524.479882342713</v>
       </c>
       <c r="G19" s="121">
-        <v>11.269027574003</v>
+        <v>11.2738743878656</v>
       </c>
       <c r="H19" s="123">
         <v>762.381084185746</v>
@@ -8833,10 +8819,8 @@
       <c r="F26" s="118">
         <v>18.039305987669</v>
       </c>
-      <c r="G26" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G26" s="120">
+        <v>0.0102791221980518</v>
       </c>
       <c r="H26" s="122">
         <v>2.22142915003283</v>
@@ -8894,10 +8878,8 @@
       <c r="F27" s="118">
         <v>128.070596281862</v>
       </c>
-      <c r="G27" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G27" s="120">
+        <v>0.084768410279486</v>
       </c>
       <c r="H27" s="122">
         <v>25.3315547959174</v>
@@ -9014,10 +8996,8 @@
       <c r="F29" s="118">
         <v>81.9896469241408</v>
       </c>
-      <c r="G29" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G29" s="120">
+        <v>0.00795490186807913</v>
       </c>
       <c r="H29" s="122">
         <v>376.268128305447</v>
@@ -9137,7 +9117,7 @@
         <v>486.663089130693</v>
       </c>
       <c r="G31" s="121">
-        <v>1.87670149733589</v>
+        <v>1.9797039316815</v>
       </c>
       <c r="H31" s="123">
         <v>693.190883701372</v>
@@ -9195,10 +9175,8 @@
       <c r="F32" s="118">
         <v>19.2966383585306</v>
       </c>
-      <c r="G32" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G32" s="120">
+        <v>0.0113576548359922</v>
       </c>
       <c r="H32" s="122">
         <v>2.59811950087483</v>
@@ -9374,10 +9352,8 @@
       <c r="F35" s="118">
         <v>73.4022745769803</v>
       </c>
-      <c r="G35" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G35" s="120">
+        <v>0.0118809701661366</v>
       </c>
       <c r="H35" s="122">
         <v>422.292821503927</v>
@@ -9497,7 +9473,7 @@
         <v>556.279624914636</v>
       </c>
       <c r="G37" s="121">
-        <v>3.30128159267445</v>
+        <v>3.32452021767658</v>
       </c>
       <c r="H37" s="123">
         <v>746.953239814174</v>
@@ -9555,10 +9531,8 @@
       <c r="F38" s="118">
         <v>18.0519139106547</v>
       </c>
-      <c r="G38" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G38" s="120">
+        <v>0.0199847074442506</v>
       </c>
       <c r="H38" s="122">
         <v>5.10136596212385</v>
@@ -9855,7 +9829,7 @@
         <v>355.521625460421</v>
       </c>
       <c r="G43" s="121">
-        <v>2.6206213171643</v>
+        <v>2.64060602460855</v>
       </c>
       <c r="H43" s="123">
         <v>824.772137533947</v>
@@ -9913,10 +9887,8 @@
       <c r="F44" s="118">
         <v>17.2229763297876</v>
       </c>
-      <c r="G44" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G44" s="120">
+        <v>0.0268331465391326</v>
       </c>
       <c r="H44" s="122">
         <v>3.5436078158104</v>
@@ -10092,10 +10064,8 @@
       <c r="F47" s="118">
         <v>89.8791893262916</v>
       </c>
-      <c r="G47" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G47" s="120">
+        <v>0.00247256120461069</v>
       </c>
       <c r="H47" s="122">
         <v>467.065416340215</v>
@@ -10215,7 +10185,7 @@
         <v>473.28174726289</v>
       </c>
       <c r="G49" s="121">
-        <v>1.03146769456108</v>
+        <v>1.06077340230483</v>
       </c>
       <c r="H49" s="123">
         <v>829.711506744594</v>
@@ -10273,10 +10243,8 @@
       <c r="F50" s="118">
         <v>18.3134723727587</v>
       </c>
-      <c r="G50" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G50" s="120">
+        <v>0.020694541454992</v>
       </c>
       <c r="H50" s="122">
         <v>2.65861918022268</v>
@@ -10334,10 +10302,8 @@
       <c r="F51" s="118">
         <v>135.575913555338</v>
       </c>
-      <c r="G51" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G51" s="120">
+        <v>0.0167330583487969</v>
       </c>
       <c r="H51" s="122">
         <v>26.5344736840675</v>
@@ -10454,10 +10420,8 @@
       <c r="F53" s="118">
         <v>102.168313208074</v>
       </c>
-      <c r="G53" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G53" s="120">
+        <v>0.00567249471797881</v>
       </c>
       <c r="H53" s="122">
         <v>460.976571537733</v>
@@ -10577,7 +10541,7 @@
         <v>523.978499627486</v>
       </c>
       <c r="G55" s="121">
-        <v>0.537540373782651</v>
+        <v>0.580640468304418</v>
       </c>
       <c r="H55" s="123">
         <v>822.729433166227</v>
